--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -1885,10 +1885,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117694676</v>
+        <v>117694688</v>
       </c>
       <c r="B12" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1897,30 +1897,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1928,10 +1933,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512454</v>
+        <v>512471</v>
       </c>
       <c r="R12" t="n">
-        <v>6728406</v>
+        <v>6728400</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117694688</v>
+        <v>117694676</v>
       </c>
       <c r="B13" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,35 +2018,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512471</v>
+        <v>512454</v>
       </c>
       <c r="R13" t="n">
-        <v>6728400</v>
+        <v>6728406</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -1885,10 +1885,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117694688</v>
+        <v>117694676</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1897,35 +1897,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1933,10 +1928,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512471</v>
+        <v>512454</v>
       </c>
       <c r="R12" t="n">
-        <v>6728400</v>
+        <v>6728406</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117694676</v>
+        <v>117694688</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2018,30 +2013,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512454</v>
+        <v>512471</v>
       </c>
       <c r="R13" t="n">
-        <v>6728406</v>
+        <v>6728400</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2120,6 +2120,131 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118060189</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56500</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>512513</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6728363</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Medobservatör tjäderexpert Göran Rönning.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -2247,10 +2247,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118326035</v>
+        <v>118328933</v>
       </c>
       <c r="B15" t="n">
-        <v>57290</v>
+        <v>57306</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2263,16 +2263,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512498</v>
+        <v>512443</v>
       </c>
       <c r="R15" t="n">
-        <v>6728445</v>
+        <v>6728401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2331,11 +2331,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,10 +2367,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118328933</v>
+        <v>118326035</v>
       </c>
       <c r="B16" t="n">
-        <v>57306</v>
+        <v>57290</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2388,16 +2383,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2420,10 +2415,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>512443</v>
+        <v>512498</v>
       </c>
       <c r="R16" t="n">
-        <v>6728401</v>
+        <v>6728445</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2456,6 +2451,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119870466</v>
+        <v>119870403</v>
       </c>
       <c r="B19" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2747,35 +2747,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2790,7 +2790,7 @@
         <v>6728413</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2817,19 +2817,9 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2861,10 +2851,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119870403</v>
+        <v>119870466</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2873,35 +2863,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2916,7 +2906,7 @@
         <v>6728413</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2943,9 +2933,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119870403</v>
+        <v>119870466</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>57473</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2747,35 +2747,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2790,7 +2790,7 @@
         <v>6728413</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2817,9 +2817,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2851,10 +2861,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119870466</v>
+        <v>119870403</v>
       </c>
       <c r="B20" t="n">
-        <v>57463</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2863,35 +2873,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2906,7 +2916,7 @@
         <v>6728413</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2933,19 +2943,9 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119870466</v>
+        <v>119870403</v>
       </c>
       <c r="B19" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2747,35 +2747,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2790,7 +2790,7 @@
         <v>6728413</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2817,19 +2817,9 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2861,10 +2851,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119870403</v>
+        <v>119870466</v>
       </c>
       <c r="B20" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2873,35 +2863,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2916,7 +2906,7 @@
         <v>6728413</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2943,9 +2933,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119870403</v>
+        <v>119870466</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2747,35 +2747,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2790,7 +2790,7 @@
         <v>6728413</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2817,9 +2817,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2851,10 +2861,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119870466</v>
+        <v>119870403</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2863,35 +2873,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2906,7 +2916,7 @@
         <v>6728413</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2933,19 +2943,9 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -1779,7 +1779,7 @@
         <v>116451640</v>
       </c>
       <c r="B11" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2868,10 +2868,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121111866</v>
+        <v>121111998</v>
       </c>
       <c r="B20" t="n">
-        <v>78598</v>
+        <v>56563</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2880,30 +2880,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2911,10 +2916,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512493</v>
+        <v>512453</v>
       </c>
       <c r="R20" t="n">
-        <v>6728416</v>
+        <v>6728417</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2949,13 +2954,17 @@
           <t>2024-11-08</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Sandbad samt fjäder från tupp.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2984,10 +2993,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121111998</v>
+        <v>121112047</v>
       </c>
       <c r="B21" t="n">
-        <v>56560</v>
+        <v>90697</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2996,35 +3005,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3032,10 +3036,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512453</v>
+        <v>512426</v>
       </c>
       <c r="R21" t="n">
-        <v>6728417</v>
+        <v>6728398</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3070,17 +3074,13 @@
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Sandbad samt fjäder från tupp.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121112047</v>
+        <v>121111866</v>
       </c>
       <c r="B22" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512426</v>
+        <v>512493</v>
       </c>
       <c r="R22" t="n">
-        <v>6728398</v>
+        <v>6728416</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -2868,10 +2868,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121111998</v>
+        <v>121112047</v>
       </c>
       <c r="B20" t="n">
-        <v>56563</v>
+        <v>90697</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2880,35 +2880,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2916,10 +2911,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512453</v>
+        <v>512426</v>
       </c>
       <c r="R20" t="n">
-        <v>6728417</v>
+        <v>6728398</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2954,17 +2949,13 @@
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Sandbad samt fjäder från tupp.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2993,10 +2984,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121112047</v>
+        <v>121111998</v>
       </c>
       <c r="B21" t="n">
-        <v>90697</v>
+        <v>56563</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3005,30 +2996,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3036,10 +3032,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512426</v>
+        <v>512453</v>
       </c>
       <c r="R21" t="n">
-        <v>6728398</v>
+        <v>6728417</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3074,13 +3070,17 @@
           <t>2024-11-08</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Sandbad samt fjäder från tupp.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -1779,7 +1779,7 @@
         <v>116451640</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2868,10 +2868,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121112047</v>
+        <v>121111866</v>
       </c>
       <c r="B20" t="n">
-        <v>90697</v>
+        <v>78604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2884,21 +2884,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512426</v>
+        <v>512493</v>
       </c>
       <c r="R20" t="n">
-        <v>6728398</v>
+        <v>6728416</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121111998</v>
+        <v>121112047</v>
       </c>
       <c r="B21" t="n">
-        <v>56563</v>
+        <v>90709</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2996,35 +2996,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3032,10 +3027,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512453</v>
+        <v>512426</v>
       </c>
       <c r="R21" t="n">
-        <v>6728417</v>
+        <v>6728398</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3070,17 +3065,13 @@
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Sandbad samt fjäder från tupp.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3109,10 +3100,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121111866</v>
+        <v>121111998</v>
       </c>
       <c r="B22" t="n">
-        <v>78601</v>
+        <v>56563</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3121,30 +3112,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3152,10 +3148,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512493</v>
+        <v>512453</v>
       </c>
       <c r="R22" t="n">
-        <v>6728416</v>
+        <v>6728417</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3190,13 +3186,17 @@
           <t>2024-11-08</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Sandbad samt fjäder från tupp.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -1779,7 +1779,7 @@
         <v>116451640</v>
       </c>
       <c r="B11" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2868,10 +2868,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121111866</v>
+        <v>121111998</v>
       </c>
       <c r="B20" t="n">
-        <v>78604</v>
+        <v>56563</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2880,30 +2880,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2911,10 +2916,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512493</v>
+        <v>512453</v>
       </c>
       <c r="R20" t="n">
-        <v>6728416</v>
+        <v>6728417</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2949,13 +2954,17 @@
           <t>2024-11-08</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Sandbad samt fjäder från tupp.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2984,10 +2993,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121112047</v>
+        <v>121111866</v>
       </c>
       <c r="B21" t="n">
-        <v>90709</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3000,21 +3009,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3027,10 +3036,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512426</v>
+        <v>512493</v>
       </c>
       <c r="R21" t="n">
-        <v>6728398</v>
+        <v>6728416</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3100,10 +3109,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121111998</v>
+        <v>121112047</v>
       </c>
       <c r="B22" t="n">
-        <v>56563</v>
+        <v>90710</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3112,35 +3121,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3148,10 +3152,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512453</v>
+        <v>512426</v>
       </c>
       <c r="R22" t="n">
-        <v>6728417</v>
+        <v>6728398</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3186,17 +3190,13 @@
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Sandbad samt fjäder från tupp.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -1779,7 +1779,7 @@
         <v>116451640</v>
       </c>
       <c r="B11" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2868,10 +2868,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121111998</v>
+        <v>121112047</v>
       </c>
       <c r="B20" t="n">
-        <v>56563</v>
+        <v>90713</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2880,35 +2880,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2916,10 +2911,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512453</v>
+        <v>512426</v>
       </c>
       <c r="R20" t="n">
-        <v>6728417</v>
+        <v>6728398</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2954,17 +2949,13 @@
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Sandbad samt fjäder från tupp.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2993,10 +2984,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121111866</v>
+        <v>121111998</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
+        <v>56566</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3005,30 +2996,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3036,10 +3032,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512493</v>
+        <v>512453</v>
       </c>
       <c r="R21" t="n">
-        <v>6728416</v>
+        <v>6728417</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3074,13 +3070,17 @@
           <t>2024-11-08</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Sandbad samt fjäder från tupp.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121112047</v>
+        <v>121111866</v>
       </c>
       <c r="B22" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512426</v>
+        <v>512493</v>
       </c>
       <c r="R22" t="n">
-        <v>6728398</v>
+        <v>6728416</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -2984,10 +2984,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121111998</v>
+        <v>121111866</v>
       </c>
       <c r="B21" t="n">
-        <v>56566</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2996,35 +2996,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3032,10 +3027,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512453</v>
+        <v>512493</v>
       </c>
       <c r="R21" t="n">
-        <v>6728417</v>
+        <v>6728416</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3070,17 +3065,13 @@
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Sandbad samt fjäder från tupp.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3109,10 +3100,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121111866</v>
+        <v>121111998</v>
       </c>
       <c r="B22" t="n">
-        <v>78607</v>
+        <v>56566</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3121,30 +3112,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3152,10 +3148,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512493</v>
+        <v>512453</v>
       </c>
       <c r="R22" t="n">
-        <v>6728416</v>
+        <v>6728417</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3190,13 +3186,17 @@
           <t>2024-11-08</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Sandbad samt fjäder från tupp.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3223,6 +3223,131 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121550353</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98099</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>512472</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6728425</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lisa Olson, Göran Ehn, Cecilia Rastad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -3228,7 +3228,7 @@
         <v>121550353</v>
       </c>
       <c r="B23" t="n">
-        <v>98099</v>
+        <v>98104</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -3228,7 +3228,7 @@
         <v>121550353</v>
       </c>
       <c r="B23" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -3228,7 +3228,7 @@
         <v>121550353</v>
       </c>
       <c r="B23" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 57812-2023 artfynd.xlsx
+++ b/artfynd/A 57812-2023 artfynd.xlsx
@@ -2390,7 +2390,7 @@
         <v>118326035</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
